--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.462753905769516</v>
+        <v>0.4001975096875464</v>
       </c>
       <c r="D2" t="n">
-        <v>55.38989188883464</v>
+        <v>9.000857431935628</v>
       </c>
       <c r="E2" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F2" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.55322470573935</v>
+        <v>4.152399014682643</v>
       </c>
       <c r="D3" t="n">
-        <v>34.1700906881571</v>
+        <v>5.55263973682553</v>
       </c>
       <c r="E3" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F3" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.85856446077045</v>
+        <v>5.177016724875197</v>
       </c>
       <c r="D4" t="n">
-        <v>27.17275503529538</v>
+        <v>4.415572693235499</v>
       </c>
       <c r="E4" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F4" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.14589798172901</v>
+        <v>6.036208422030965</v>
       </c>
       <c r="D5" t="n">
-        <v>22.13308690084733</v>
+        <v>3.596626621387692</v>
       </c>
       <c r="E5" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F5" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.94106067851907</v>
+        <v>5.515422360259349</v>
       </c>
       <c r="D6" t="n">
-        <v>11.54877230690274</v>
+        <v>1.876675499871695</v>
       </c>
       <c r="E6" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F6" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.12593699035413</v>
+        <v>3.920464760932546</v>
       </c>
       <c r="D7" t="n">
-        <v>16.64256719659651</v>
+        <v>2.704417169446932</v>
       </c>
       <c r="E7" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F7" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.9998257566483</v>
+        <v>3.899971685455349</v>
       </c>
       <c r="D8" t="n">
-        <v>16.73529660768202</v>
+        <v>2.719485698748328</v>
       </c>
       <c r="E8" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F8" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>13.35924693753347</v>
+        <v>2.170877627349189</v>
       </c>
       <c r="D9" t="n">
-        <v>14.73186267169831</v>
+        <v>2.393927684150975</v>
       </c>
       <c r="E9" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F9" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>11.16168630608525</v>
+        <v>1.813774024738854</v>
       </c>
       <c r="D10" t="n">
-        <v>11.12985773641089</v>
+        <v>1.80860188216677</v>
       </c>
       <c r="E10" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F10" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>6.93923801089502</v>
+        <v>1.127626176770441</v>
       </c>
       <c r="D11" t="n">
-        <v>30.01666203960727</v>
+        <v>4.877707581436181</v>
       </c>
       <c r="E11" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F11" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>10.75839625005856</v>
+        <v>1.748239390634516</v>
       </c>
       <c r="D12" t="n">
-        <v>28.77835053088446</v>
+        <v>4.676481961268724</v>
       </c>
       <c r="E12" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F12" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>15.3163233199009</v>
+        <v>2.488902539483896</v>
       </c>
       <c r="D13" t="n">
-        <v>15.17120803089743</v>
+        <v>2.465321305020832</v>
       </c>
       <c r="E13" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F13" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.4797881319489</v>
+        <v>4.952965571441696</v>
       </c>
       <c r="D14" t="n">
-        <v>31.71030458508129</v>
+        <v>5.15292449507571</v>
       </c>
       <c r="E14" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F14" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>35.83411693536539</v>
+        <v>5.823044001996876</v>
       </c>
       <c r="D15" t="n">
-        <v>38.86037510876874</v>
+        <v>6.314810955174921</v>
       </c>
       <c r="E15" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F15" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>27.53062976474421</v>
+        <v>4.473727336770933</v>
       </c>
       <c r="D16" t="n">
-        <v>47.18738874417181</v>
+        <v>7.66795067092792</v>
       </c>
       <c r="E16" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F16" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>34.48088873714385</v>
+        <v>5.603144419785876</v>
       </c>
       <c r="D17" t="n">
-        <v>45.9850758855641</v>
+        <v>7.472574831404167</v>
       </c>
       <c r="E17" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F17" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24720286242822</v>
+        <v>5.565170465144587</v>
       </c>
       <c r="D18" t="n">
-        <v>34.0801109517409</v>
+        <v>5.538018029657897</v>
       </c>
       <c r="E18" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F18" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31.94402684464697</v>
+        <v>5.190904362255133</v>
       </c>
       <c r="D19" t="n">
-        <v>50.42154477701654</v>
+        <v>8.193501026265187</v>
       </c>
       <c r="E19" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F19" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>39.15430850818893</v>
+        <v>6.362575132580701</v>
       </c>
       <c r="D20" t="n">
-        <v>62.1456373924476</v>
+        <v>10.09866607627274</v>
       </c>
       <c r="E20" t="n">
-        <v>11.02844027355233</v>
+        <v>1.792121544452254</v>
       </c>
       <c r="F20" t="n">
-        <v>15.05493297134294</v>
+        <v>2.446426607843228</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
